--- a/MetaData/Tirreno-Adriatico.xlsx
+++ b/MetaData/Tirreno-Adriatico.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="10"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" firstSheet="6" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="2009" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="259">
   <si>
     <t>NUM</t>
   </si>
@@ -514,9 +514,6 @@
     <t>1028.18 Km</t>
   </si>
   <si>
-    <t>P</t>
-  </si>
-  <si>
     <t>Wednesday 11 March 2015</t>
   </si>
   <si>
@@ -806,6 +803,10 @@
   </si>
   <si>
     <t>1050.49 Km</t>
+  </si>
+  <si>
+    <t>NUM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1557,13 +1558,13 @@
         <v>77</v>
       </c>
       <c r="C2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D2" t="s">
         <v>220</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>221</v>
-      </c>
-      <c r="E2" t="s">
-        <v>222</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1586,13 +1587,13 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D3" t="s">
         <v>223</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>224</v>
-      </c>
-      <c r="E3" t="s">
-        <v>225</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1615,13 +1616,13 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
+        <v>225</v>
+      </c>
+      <c r="D4" t="s">
         <v>226</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>227</v>
-      </c>
-      <c r="E4" t="s">
-        <v>228</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1644,13 +1645,13 @@
         <v>29</v>
       </c>
       <c r="C5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D5" t="s">
         <v>229</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>230</v>
-      </c>
-      <c r="E5" t="s">
-        <v>231</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1673,13 +1674,13 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
+        <v>231</v>
+      </c>
+      <c r="D6" t="s">
         <v>232</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>233</v>
-      </c>
-      <c r="E6" t="s">
-        <v>234</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1702,13 +1703,13 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
+        <v>234</v>
+      </c>
+      <c r="D7" t="s">
         <v>235</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>236</v>
-      </c>
-      <c r="E7" t="s">
-        <v>237</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1731,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D8" t="s">
         <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1757,7 +1758,7 @@
         <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -1944,13 +1945,13 @@
         <v>77</v>
       </c>
       <c r="C2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E2" t="s">
         <v>241</v>
-      </c>
-      <c r="D2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E2" t="s">
-        <v>242</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1973,13 +1974,13 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" t="s">
         <v>243</v>
-      </c>
-      <c r="D3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E3" t="s">
-        <v>244</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -2002,13 +2003,13 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D4" t="s">
         <v>245</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>246</v>
-      </c>
-      <c r="E4" t="s">
-        <v>247</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -2031,13 +2032,13 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D5" t="s">
         <v>248</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>249</v>
-      </c>
-      <c r="E5" t="s">
-        <v>250</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -2060,13 +2061,13 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
+        <v>250</v>
+      </c>
+      <c r="D6" t="s">
         <v>251</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>252</v>
-      </c>
-      <c r="E6" t="s">
-        <v>253</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -2089,13 +2090,13 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D7" t="s">
         <v>254</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>255</v>
-      </c>
-      <c r="E7" t="s">
-        <v>256</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -2118,13 +2119,13 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D8" t="s">
         <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -2144,7 +2145,7 @@
         <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -4231,7 +4232,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -4259,20 +4260,20 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>161</v>
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
       </c>
       <c r="C2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D2" t="s">
         <v>162</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>163</v>
-      </c>
-      <c r="E2" t="s">
-        <v>164</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4289,19 +4290,19 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D3" t="s">
         <v>165</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>166</v>
-      </c>
-      <c r="E3" t="s">
-        <v>167</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -4318,19 +4319,19 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D4" t="s">
         <v>147</v>
       </c>
       <c r="E4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -4347,19 +4348,19 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D5" t="s">
         <v>170</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>171</v>
-      </c>
-      <c r="E5" t="s">
-        <v>172</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -4376,19 +4377,19 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
       </c>
       <c r="C6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D6" t="s">
         <v>173</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>174</v>
-      </c>
-      <c r="E6" t="s">
-        <v>175</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -4405,19 +4406,19 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D7" t="s">
         <v>176</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>177</v>
-      </c>
-      <c r="E7" t="s">
-        <v>178</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -4434,13 +4435,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D8" t="s">
         <v>34</v>
@@ -4466,7 +4467,7 @@
         <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -4653,13 +4654,13 @@
         <v>77</v>
       </c>
       <c r="C2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E2" t="s">
         <v>181</v>
-      </c>
-      <c r="D2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E2" t="s">
-        <v>182</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4682,13 +4683,13 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D3" t="s">
         <v>183</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>184</v>
-      </c>
-      <c r="E3" t="s">
-        <v>185</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -4711,13 +4712,13 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D4" t="s">
         <v>186</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>187</v>
-      </c>
-      <c r="E4" t="s">
-        <v>188</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -4740,13 +4741,13 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D5" t="s">
         <v>189</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>190</v>
-      </c>
-      <c r="E5" t="s">
-        <v>191</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -4769,13 +4770,13 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D6" t="s">
         <v>192</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>193</v>
-      </c>
-      <c r="E6" t="s">
-        <v>194</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -4798,13 +4799,13 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D7" t="s">
         <v>195</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>196</v>
-      </c>
-      <c r="E7" t="s">
-        <v>197</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -4827,13 +4828,13 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D8" t="s">
         <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -4853,7 +4854,7 @@
         <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -5040,13 +5041,13 @@
         <v>77</v>
       </c>
       <c r="C2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E2" t="s">
         <v>201</v>
-      </c>
-      <c r="D2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E2" t="s">
-        <v>202</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -5069,13 +5070,13 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" t="s">
         <v>203</v>
-      </c>
-      <c r="D3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E3" t="s">
-        <v>204</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -5098,13 +5099,13 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D4" t="s">
         <v>205</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>206</v>
-      </c>
-      <c r="E4" t="s">
-        <v>207</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -5127,13 +5128,13 @@
         <v>29</v>
       </c>
       <c r="C5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D5" t="s">
         <v>208</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>209</v>
-      </c>
-      <c r="E5" t="s">
-        <v>210</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -5156,13 +5157,13 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D6" t="s">
         <v>211</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>212</v>
-      </c>
-      <c r="E6" t="s">
-        <v>213</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -5185,13 +5186,13 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
+        <v>213</v>
+      </c>
+      <c r="D7" t="s">
         <v>214</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>215</v>
-      </c>
-      <c r="E7" t="s">
-        <v>216</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -5214,13 +5215,13 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D8" t="s">
         <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -5240,7 +5241,7 @@
         <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
